--- a/tests/sample_data/CatchByOYF.xlsx
+++ b/tests/sample_data/CatchByOYF.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -370,25 +370,1394 @@
           <t>...3</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>...4</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>...5</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>...6</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>...7</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>...8</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>...9</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>...10</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>...11</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>...12</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>...13</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Catches are presented as whole weights in tonnes.  All figures, particularly for the last reported year of catch are subject to change as improved data or estimates become available.</t>
+          <t>Atlantic</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1051.4351635277101</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Atlantic</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6528.0315064359202</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Note:  reviews of SBT data in 2006 indicated that southern bluefin tuna catches may have been substantially under-reported over the previous 10-20 years and the data presented here do not yet include estimates for this unreported catch.</t>
+          <t>Atlantic</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>908.608206108427</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>102.96069415300001</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Atlantic</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>68.129633106768495</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4.2060295840000004</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>16.946410389</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22.6067</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Atlantic</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1524.75137313554</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1191.3414507949999</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4.3147542449999996</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>96.521203145000001</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3410.6390225772002</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>23137.560073552999</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13299.3888623642</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>18934.858793135099</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>243.40499756700001</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2.9885299999999999</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4512.5562831838897</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2868.9403555722201</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>12.4297908178934</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>850.03977461099998</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1369.9978900000001</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>14.685499999999999</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4692.5550659999999</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3153.3981085095402</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>643.38930585100002</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1121.2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>79.485699999999994</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1700.7849699999999</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>203.251</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>7.0692000000000004</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5813.4609298134601</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1928.6299548104</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>157.06375120999999</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>956.70804850499997</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>64.974999999999994</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>564.67241000000001</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3.3650000000000002</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.254600000000003</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>8.8282000000000007</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5628.7490699999998</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3444.9071151714802</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>148.905879556</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>845.21262958299997</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>50.406799999999997</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>597.88905999999997</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>12.641400000000001</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3.7055899999999999</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4444.41270008017</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1394.33009078291</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>641.81846751600006</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>469.59510430300003</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>45.5032</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>909.755</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>95.624099999999999</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.32490000000000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5256.2087235095796</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1712.3666865144501</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>275.35156348800001</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1139.907776003</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>592.94899999999996</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>16.1982</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4198.5093473829402</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2891.7780817609701</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>920.619585132</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1112.524106118</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1297.66805</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>20.810894145999999</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.23860000000000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6559.4517947452296</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>12466.027997507001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.79694824032368905</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1094.67254338713</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>613.07858434294405</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1260.1512839371901</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>164.48299999899999</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>231.557317966</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>453.78098380501501</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1510.41549102161</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>276.99400000200001</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>580.72880618254203</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1634.40179657986</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>951.97300000200005</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2.2057115199999999</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>979.60171700439798</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2332.4822105492199</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>935.20700000099998</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
